--- a/artfynd/A 44402-2025 artfynd.xlsx
+++ b/artfynd/A 44402-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125096081</v>
+        <v>125096080</v>
       </c>
       <c r="B2" t="n">
-        <v>78967</v>
+        <v>91872</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>469776</v>
+        <v>469767</v>
       </c>
       <c r="R2" t="n">
-        <v>6650780</v>
+        <v>6650770</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -787,14 +787,14 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125096082</v>
+        <v>125096075</v>
       </c>
       <c r="B3" t="n">
-        <v>78967</v>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>469787</v>
+        <v>469766</v>
       </c>
       <c r="R3" t="n">
-        <v>6650777</v>
+        <v>6650703</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -899,14 +899,14 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125096083</v>
+        <v>125096076</v>
       </c>
       <c r="B4" t="n">
-        <v>78967</v>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -934,10 +934,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>469786</v>
+        <v>469762</v>
       </c>
       <c r="R4" t="n">
-        <v>6650784</v>
+        <v>6650702</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1011,32 +1011,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125096080</v>
+        <v>125096077</v>
       </c>
       <c r="B5" t="n">
-        <v>91185</v>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1046,10 +1046,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>469767</v>
+        <v>469751</v>
       </c>
       <c r="R5" t="n">
-        <v>6650770</v>
+        <v>6650708</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1123,14 +1123,14 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125096079</v>
+        <v>125096078</v>
       </c>
       <c r="B6" t="n">
-        <v>78967</v>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -1158,10 +1158,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>469751</v>
+        <v>469747</v>
       </c>
       <c r="R6" t="n">
-        <v>6650740</v>
+        <v>6650717</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1235,14 +1235,14 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125096077</v>
+        <v>125096079</v>
       </c>
       <c r="B7" t="n">
-        <v>78967</v>
+        <v>79327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -1273,7 +1273,7 @@
         <v>469751</v>
       </c>
       <c r="R7" t="n">
-        <v>6650708</v>
+        <v>6650740</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1347,14 +1347,14 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125096075</v>
+        <v>125096081</v>
       </c>
       <c r="B8" t="n">
-        <v>78967</v>
+        <v>79327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -1382,10 +1382,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>469766</v>
+        <v>469776</v>
       </c>
       <c r="R8" t="n">
-        <v>6650703</v>
+        <v>6650780</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1459,14 +1459,14 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125096078</v>
+        <v>125096082</v>
       </c>
       <c r="B9" t="n">
-        <v>78967</v>
+        <v>79327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -1494,10 +1494,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>469747</v>
+        <v>469787</v>
       </c>
       <c r="R9" t="n">
-        <v>6650717</v>
+        <v>6650777</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1571,14 +1571,14 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125096076</v>
+        <v>125096083</v>
       </c>
       <c r="B10" t="n">
-        <v>78967</v>
+        <v>79327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -1606,10 +1606,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>469762</v>
+        <v>469786</v>
       </c>
       <c r="R10" t="n">
-        <v>6650702</v>
+        <v>6650784</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>

--- a/artfynd/A 44402-2025 artfynd.xlsx
+++ b/artfynd/A 44402-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AZ10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -784,6 +789,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125096080</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -896,6 +906,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125096075</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1008,6 +1023,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125096076</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1120,6 +1140,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125096077</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1232,6 +1257,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125096078</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1344,6 +1374,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125096079</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1456,6 +1491,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125096081</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1568,6 +1608,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125096082</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1680,8 +1725,24 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125096083</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>